--- a/llm_reliability_annotation_package/sampled_contexts_for_human_annotation.xlsx
+++ b/llm_reliability_annotation_package/sampled_contexts_for_human_annotation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\数据集\new\shujudingjia\llm_reliability_annotation_package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6EC26C-3400-41F0-860C-F557C77FF237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30284935-B55B-4350-91BA-A13A4BD9D283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="411">
   <si>
     <t>sample_id</t>
   </si>
@@ -159,9 +159,6 @@
     <t>S002__Data Market Design A Systematic Literature Review.pdf</t>
   </si>
   <si>
-    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S002__Data Market Design A Systematic Literature Review.pdf</t>
-  </si>
-  <si>
     <t>S003</t>
   </si>
   <si>
@@ -211,98 +208,87 @@
     <t>A Survey on Data Pricing: From Economics to Data Science</t>
   </si>
   <si>
-    <t>transaction industry. Big data empowers business value, leads to signiﬁcant changes, and even becomes a driving factor for business model innovation. According to the report from International Data Corporation, the worldwide revenue of big data analysis markets will grow up to $260 billion in 2022 [1]. However, using data to generate business value in many scenarios needs further improvement. For small organizations, insufﬁcient data will hinder the establishment of better models and can not meet the needs of analysis, application and decision support [2]. Recent studies and prac tices have appr_x000D_
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>0.2351999999999999</t>
+  </si>
+  <si>
+    <t>S004__Data Boundary and Data Pricing Based on the Shapley Value.pdf</t>
+  </si>
+  <si>
+    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S004__Data Boundary and Data Pricing Based on the Shapley Value.pdf</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>W3202603574-&gt;W2974598553</t>
+  </si>
+  <si>
+    <t>W3202603574</t>
+  </si>
+  <si>
+    <t>W2974598553</t>
+  </si>
+  <si>
+    <t>COVID-19 acceleration in digitalisation, aggregate productivity growth and the functional income distribution</t>
+  </si>
+  <si>
+    <t>Too Much Data: Prices and Inefficiencies in Data Markets</t>
+  </si>
+  <si>
+    <t>e productivity and output; (2) what are the possible effects on the functional income distribution, i.e. how are profits, wages and digital skill premia affected; and (3) what could be possible policy responses? 1 Combined, the four companies Google, Amazon, Facebook and Apple reach a market capitalisa tion value of nearly $5.5 trillion in November 2020 entailing nearly 40% growth up from $4 trillion in December 2019 and a 50% growth on average since March 2020.Yahoo Finance; https://​www.​techc​han nel.​news/​11/​11/​2020/​market ​cap ​of ​big ​five ​tech ​compa​nies ​surge ​46 ​to 7 ​1tr ​so ​far ​this ​year/; https://​ compa​niesm​arket​cap.​com/​tech/​large​st ​tech ​compa​nies ​by ​market ​cap/ and https:/_x000D_
 _x000D_
 ... [另一次引用] ..._x000D_
 _x000D_
-ng point zi 1: Initialize SVi = 0 for i = 1, . . . , N and t = 0 2: while Convergence criteria not met do 3: t ←t + 1 4: πt: Random permutation of train data points 5: vt 0 ←V(zi, A) 6: for j ∈{1, . . . , N} do 7: if V(D) −vt j−1 &lt; Performance Tolerance then 8: vt j = vt j−1 9: else 10: vt j = V({πt[1], . . . , πt[j]}, A) 11: end if 12: SVπt[j] ←t−1 t SVπt−1[j] + 1 t (vt j −vt j−1) 13: end for 14: end while • Monotonicity: Given a function f : (R+)k →R+, it is monotone if and only if for any two vectors x, y ∈ (R+)k : x ≤y, we have f (x) ≤f (y); • Subadditivity: Given a function f : (R+)k →R+, it_x000D_
+erial capital. This may explain the growing productivity divide between fron tier firms and laggards (see e.g. Berlingieri et al. 2020; Andrews et al. 2018). Also, (b) being a general purpose technology,4 a critical mass of ICT penetration may be required before aggregate productivity gains materialise. (Anderton et al. 2020; Brynjolfsson et al. 2019; Cardona et al. 2013). Van Ark et al. (2019) point to above average contributions to productivity growth from the most ICT intensive industries. A finding very relevant for our paper is that the concentration of activity in the most productive firms (‘superstar firms’) drives not only an increase i_x000D_
 _x000D_
 ... [另一次引用] ..._x000D_
 _x000D_
-ods according to real time demand. It is necessary to explore the dynamic pricing mechanism with the utilize of machine learning. Finally, there is only one broker in our market, but multiple brokers co exist in practical applications, and the versions of models can be further optimized. REFERENCES [1] J. Y. Cheng and P. W. Dong, ‘‘Thinking of corporation ﬁnancial manage ment innovation in the era of big data,’’ in Proc. Int. Conf. Manage. Sci. Manage. Innov. Paris, France: Atlantis Press, 2015, pp. 450 455. [2] R. Raskar, P. Vepakomma, T. Swedish, and A. Sharan, ‘‘Data mar kets to support AI for</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>0.2351999999999999</t>
-  </si>
-  <si>
-    <t>S004__Data Boundary and Data Pricing Based on the Shapley Value.pdf</t>
-  </si>
-  <si>
-    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S004__Data Boundary and Data Pricing Based on the Shapley Value.pdf</t>
-  </si>
-  <si>
-    <t>S005</t>
-  </si>
-  <si>
-    <t>W3202603574-&gt;W2974598553</t>
-  </si>
-  <si>
-    <t>W3202603574</t>
-  </si>
-  <si>
-    <t>W2974598553</t>
-  </si>
-  <si>
-    <t>COVID-19 acceleration in digitalisation, aggregate productivity growth and the functional income distribution</t>
-  </si>
-  <si>
-    <t>Too Much Data: Prices and Inefficiencies in Data Markets</t>
-  </si>
-  <si>
-    <t>e productivity and output; (2) what are the possible effects on the functional income distribution, i.e. how are profits, wages and digital skill premia affected; and (3) what could be possible policy responses? 1 Combined, the four companies Google, Amazon, Facebook and Apple reach a market capitalisa tion value of nearly $5.5 trillion in November 2020 entailing nearly 40% growth up from $4 trillion in December 2019 and a 50% growth on average since March 2020.Yahoo Finance; https://​www.​techc​han nel.​news/​11/​11/​2020/​market ​cap ​of ​big ​five ​tech ​compa​nies ​surge ​46 ​to 7 ​1tr ​so ​far ​this ​year/; https://​ compa​niesm​arket​cap.​com/​tech/​large​st ​tech ​compa​nies ​by ​market ​cap/ and https:/_x000D_
+eign competition, domestic labour demand may increase across skills groups (Aghion et al. 2019). Different manifestations of ICT may have different effects. Acemoglu and Restrepo (2017) find that industrial robots reduce employment, while other forms of ICT do not. Similarly, based on a survey of Swiss firms, Balsmeier and Woerter (2019) observe increases (decreases) in the demand for high skilled (low skilled) workers related to ICT. These effects largely stem from machine based ICT such as robots, but not from e commerce. 575 COVID 19 acceleration in digitalisation, aggregate… 1 3 High skills are an important asset but to reap t</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>0.1584375</t>
+  </si>
+  <si>
+    <t>S005__COVID-19 acceleration in digitalisation, aggregate productivity growth and the f.pdf</t>
+  </si>
+  <si>
+    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S005__COVID-19 acceleration in digitalisation, aggregate productivity growth and the f.pdf</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>W3186955607-&gt;W2018362551</t>
+  </si>
+  <si>
+    <t>W3186955607</t>
+  </si>
+  <si>
+    <t>W2018362551</t>
+  </si>
+  <si>
+    <t>Pricing through health apps generated data—Digital dividend as a game changer: Discrete choice experiment</t>
+  </si>
+  <si>
+    <t>The challenges of personal data markets and privacy</t>
+  </si>
+  <si>
+    <t>roving treat ment quality, preventive care, and diagnostics [13]. Hence, research about incentive systems to trigger a large and diverse group of users to share their data for R&amp;D purposes is essential. Bataineh et al. criticized the market for personal data because it shows a significant imbalance [15]. App users are currently not compensated for the provision of their data, and the authors further criticized the lack of an adequate platform to monetize and trade self tracked data [15]. The question about the compensation that people are willing to accept remains unsolved. This is despite the fac_x000D_
 _x000D_
 ... [另一次引用] ..._x000D_
 _x000D_
-erial capital. This may explain the growing productivity divide between fron tier firms and laggards (see e.g. Berlingieri et al. 2020; Andrews et al. 2018). Also, (b) being a general purpose technology,4 a critical mass of ICT penetration may be required before aggregate productivity gains materialise. (Anderton et al. 2020; Brynjolfsson et al. 2019; Cardona et al. 2013). Van Ark et al. (2019) point to above average contributions to productivity growth from the most ICT intensive industries. A finding very relevant for our paper is that the concentration of activity in the most productive firms (‘superstar firms’) drives not only an increase i_x000D_
-_x000D_
-... [另一次引用] ..._x000D_
-_x000D_
-eign competition, domestic labour demand may increase across skills groups (Aghion et al. 2019). Different manifestations of ICT may have different effects. Acemoglu and Restrepo (2017) find that industrial robots reduce employment, while other forms of ICT do not. Similarly, based on a survey of Swiss firms, Balsmeier and Woerter (2019) observe increases (decreases) in the demand for high skilled (low skilled) workers related to ICT. These effects largely stem from machine based ICT such as robots, but not from e commerce. 575 COVID 19 acceleration in digitalisation, aggregate… 1 3 High skills are an important asset but to reap t</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>0.1584375</t>
-  </si>
-  <si>
-    <t>S005__COVID-19 acceleration in digitalisation, aggregate productivity growth and the f.pdf</t>
-  </si>
-  <si>
-    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S005__COVID-19 acceleration in digitalisation, aggregate productivity growth and the f.pdf</t>
-  </si>
-  <si>
-    <t>S006</t>
-  </si>
-  <si>
-    <t>W3186955607-&gt;W2018362551</t>
-  </si>
-  <si>
-    <t>W3186955607</t>
-  </si>
-  <si>
-    <t>W2018362551</t>
-  </si>
-  <si>
-    <t>Pricing through health apps generated data—Digital dividend as a game changer: Discrete choice experiment</t>
-  </si>
-  <si>
-    <t>The challenges of personal data markets and privacy</t>
-  </si>
-  <si>
-    <t>roving treat ment quality, preventive care, and diagnostics [13]. Hence, research about incentive systems to trigger a large and diverse group of users to share their data for R&amp;D purposes is essential. Bataineh et al. criticized the market for personal data because it shows a significant imbalance [15]. App users are currently not compensated for the provision of their data, and the authors further criticized the lack of an adequate platform to monetize and trade self tracked data [15]. The question about the compensation that people are willing to accept remains unsolved. This is despite the fac_x000D_
-_x000D_
-... [另一次引用] ..._x000D_
-_x000D_
 s is essential. Bataineh et al. criticized the market for personal data because it shows a significant imbalance [15]. App users are currently not compensated for the provision of their data, and the authors further criticized the lack of an adequate platform to monetize and trade self tracked data [15]. The question about the compensation that people are willing to accept remains unsolved. This is despite the fact that there have already been some research attempts at answering this ques tion, as described in the following section. However, an SADR study, i.e. a well aligned, trade off based appr</t>
   </si>
   <si>
@@ -328,13 +314,6 @@
   </si>
   <si>
     <t>Smart Contract Based Data Trading Mode Using Blockchain and Machine Learning</t>
-  </si>
-  <si>
-    <t>I. INTRODUCTION As many new technologies are integrated into our daily life, such as the mobile and the social network applications, and the smart systems based on the Internet of Things (IoT) (smart home, smart city, smart transportation, smart grid, etc.), a large amount of data will be collected [1]. We have entered the era of big data, the data sharing and trading is the trend of the times and the inevitable demand of the market. As people pay more and more attention to the economic value of big data in improving the utility efficiency and the decision making, the customer experience and othe_x000D_
-_x000D_
-... [另一次引用] ..._x000D_
-_x000D_
-resale contract is the solution to the problem of data resale, but signing a contract can not eliminate the problem of data resale. Therefore, we can design a smart contract to ensure that data will not be resold after sale, which will be the direction of further research in the future. REFERENCES [1] F. Liang, W. Yu, D. An, et al., “</t>
   </si>
   <si>
     <t>Introduction</t>
@@ -1430,25 +1409,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>omputing researchers to explore potential implications of treating user activities as labor via simulations [10]. For example, Jones and Tonetti simulated how granting users rights to the data they produce and allowing the data to be used across firms can maximize social gains from the data economy [39]. Others have taken a step further and recommended establishing third party intermediaries that are analogous to labor unions to facilitate the relations between subgroups of users and technology companies [10, 42]. In a similar vein, practitioners have piloted applications and platforms that allow
-... [另一次引用] ...
-2016. Not at Home on the Range: Peer Production and the Urban/Rural Divide. In Proceedings of the 2016 CHI Con ference on Human Factors in Computing Systems (San Jose, California, USA) (CHI ’16). Association for Computing Machinery, New York, NY, USA, 13 25. https://doi.org/10.1145/2858036.2858123 [39] Charles I Jones and Christopher Tonetti. 2020.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>neutral</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pricing of Data Products in Data Marketplaces</t>
+    <t>llm_reliability_annotation_package\sample_pdfs_by_sample_id\S002__Data Market Design A Systematic Literature Review.pdf</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1504,15 +1469,1293 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>result</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nonrivalry and the Economics of Data</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>omputing researchers to explore potential implications of treating user activities as labor via simulations [10]. For example, Jones and Tonetti simulated how granting users rights to the data they produce and allowing the data to be used across firms can maximize social gains from the data economy [39]. Others have taken a step further and recommended establishing third party intermediaries that are analogous to labor unions to facilitate the relations between subgroups of users and technology companies [10, 42]. In a similar vein, practitioners have piloted applications and platforms that allow
+... [另一次引用] ...
+2016. Not at Home on the Range: Peer Production and the Urban/Rural Divide. In Proceedings of the 2016 CHI Con ference on Human Factors in Computing Systems (San Jose, California, USA) (CHI ’16). Association for Computing Machinery, New York, NY, USA, 13 25. https://doi.org/10.1145/2858036.2858123 [39] Charles I Jones and Christopher Tonetti. 2020.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>transaction industry. Big data empowers business value, leads to signi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cant changes, and even becomes a driving factor for business model innovation. According to the report from International Data Corporation, the worldwide revenue of big data analysis markets will grow up to $260 billion in 2022 [1]. However, using data to generate business value in many scenarios needs further improvement. For small organizations, insuf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">cient data will hinder the establishment of better models and can not meet the needs of analysis, application and decision support [2]. Recent studies and prac tices have appr
+... [另一次引用] ...
+ng point zi 1: Initialize SVi = 0 for i = 1, . . . , N and t = 0 2: while Convergence criteria not met do 3: t ←t + 1 4: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">t: Random permutation of train data points 5: vt 0 ←V(zi, A) 6: for j ∈{1, . . . , N} do 7: if V(D) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vt j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 &lt; Performance Tolerance then 8: vt j = vt j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 9: else 10: vt j = V({</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">t[1], . . . , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t[j]}, A) 11: end if 12: SV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t[j] ←t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 t SV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1[j] + 1 t (vt j </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vt j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1) 13: end for 14: end while • Monotonicity: Given a function f : (R+)k →R+, it is monotone if and only if for any two vectors x, y ∈ (R+)k : x ≤y, we have f (x) ≤f (y); • Subadditivity: Given a function f : (R+)k →R+, it
+... [另一次引用] ...
+ods according to real time demand. It is necessary to explore the dynamic pricing mechanism with the utilize of machine learning. Finally, there is only one broker in our market, but multiple brokers co exist in practical applications, and the versions of models can be further optimized. REFERENCES [1] J. Y. Cheng and P. W. Dong, ‘‘Thinking of corporation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nancial manage ment innovation in the era of big data,’’ in Proc. Int. Conf. Manage. Sci. Manage. Innov. Paris, France: Atlantis Press, 2015, pp. 450 455. [2] R. Raskar, P. Vepakomma, T. Swedish, and A. Sharan, ‘‘Data mar kets to support AI for</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e productivity and output; (2) what are the possible effects on the functional income distribution, i.e. how are profits, wages and digital skill premia affected; and (3) what could be possible policy responses? 1 Combined, the four companies Google, Amazon, Facebook and Apple reach a market capitalisa tion value of nearly $5.5 trillion in November 2020 entailing nearly 40% growth up from $4 trillion in December 2019 and a 50% growth on average since March 2020.Yahoo Finance; https://</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>www.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>techc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>han nel.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>news/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2020/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">market </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">cap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">big </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">five </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tech </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">nies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">surge </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">46 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">to 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1tr </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">so </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">far </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">this </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>year/; https://</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> compa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>niesm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cap.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>com/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tech/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>large</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">st </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tech </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">nies </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">market </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cap/ and https:/
+... [另一次引用] ...
+erial capital. This may explain the growing productivity divide between fron tier firms and laggards (see e.g. Berlingieri et al. 2020; Andrews et al. 2018). Also, (b) being a general purpose technology,4 a critical mass of ICT penetration may be required before aggregate productivity gains materialise. (Anderton et al. 2020; Brynjolfsson et al. 2019; Cardona et al. 2013). Van Ark et al. (2019) point to above average contributions to productivity growth from the most ICT intensive industries. A finding very relevant for our paper is that the concentration of activity in the most productive firms (‘superstar firms’) drives not only an increase i
+... [另一次引用] ...
+eign competition, domestic labour demand may increase across skills groups (Aghion et al. 2019). Different manifestations of ICT may have different effects. Acemoglu and Restrepo (2017) find that industrial robots reduce employment, while other forms of ICT do not. Similarly, based on a survey of Swiss firms, Balsmeier and Woerter (2019) observe increases (decreases) in the demand for high skilled (low skilled) workers related to ICT. These effects largely stem from machine based ICT such as robots, but not from e commerce. 575 COVID 19 acceleration in digitalisation, aggregate… 1 3 High skills are an important asset but to reap t</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>introduction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>出现两次</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>results</t>
+    <t>出现一次</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>出现三次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>roving treat ment quality, preventive care, and diagnostics [13]. Hence, research about incentive systems to trigger a large and diverse group of users to share their data for R&amp;D purposes is essential. Bataineh et al. criticized the market for personal data because it shows a significant imbalance [15]. App users are currently not compensated for the provision of their data, and the authors further criticized the lack of an adequate platform to monetize and trade self tracked data [15]. The question about the compensation that people are willing to accept remains unsolved. This is despite the fac
+... [另一次引用] ...
+s is essential. Bataineh et al. criticized the market for personal data because it shows a significant imbalance [15]. App users are currently not compensated for the provision of their data, and the authors further criticized the lack of an adequate platform to monetize and trade self tracked data [15]. The question about the compensation that people are willing to accept remains unsolved. This is despite the fact that there have already been some research attempts at answering this ques tion, as described in the following section. However, an SADR study, i.e. a well aligned, trade off based appr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>discussion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>positive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I. INTRODUCTION As many new technologies are integrated into our daily life, such as the mobile and the social network applications, and the smart systems based on the Internet of Things (IoT) (smart home, smart city, smart transportation, smart grid, etc.), a large amount of data will be collected [1]. We have entered the era of big data, the data sharing and trading is the trend of the times and the inevitable demand of the market. As people pay more and more attention to the economic value of big data in improving the utility efficiency and the decision making, the customer experience and othe
+... [另一次引用] ...
+resale contract is the solution to the problem of data resale, but signing a contract can not eliminate the problem of data resale. Therefore, we can design a smart contract to ensure that data will not be resold after sale, which will be the direction of further research in the future. REFERENCES [1] F. Liang, W. Yu, D. An, et al., “</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现二次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Furthermore, with the advance ment of data analytics provided by machine learning and data mining techniques, and the computing capabilities supported by cloud and edge computing infrastructures, the potential values of the generated big data become more impressive [8], [9], [10], [11], [12], [13], [14]. Thus, big data is the impetus of the next waves of productivity growth. Nonetheless, there are a number of signi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cant challenges, including data collection, storage, analysis, sharing, updating, and others. To maximize the utility of the data collected, one viable solution is to design an effectiv
+... [另一次引用] ...
+g others. In addition, the data can have unstructured data types (images, video and audio streams, etc.). Thus, big data is massive, continuous, and comprehensive, and has a high potential commercial value thanks to advances in data analytic techniques, such as machine learning and data mining [9], [14]. Fig. 1: Three V of Big Data Notice that the terms data mining and Business Intelligence (BI) [25] are often used interchangeably to describe the 2169 3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only. Personal use is also permitted, but republication/redi
+... [另一次引用] ...
+ion awareness,” in 2013 IEEE Conference on Communications and Network Security (CNS), Oct 2013, pp. 488 492. [13] N. D. Nguyen, T. Nguyen, and S. Nahavandi, “System design per spective for human level agents using deep reinforcement learning: A survey,” IEEE Access, vol. 5, pp. 27 091 27 102, 2017. [14] H. He and E. A. Garcia, “Learning from imbalanced data,” IEEE Transactions on Knowledge and Data Engineering, vol. 21, no. 9, pp. 1263 1284, Sept 2009. [15] P. Lewis, “An ”all you can eat” price is clogging internet access,” New York Times. December, vol. 17, p. A1, 1996. [16] Y. Shen, B. Guo, Y. S</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pricing model for Big Personal Data</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A survey of smart data pricing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2019, and mobile video traf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c will account for 72% of the total mobile data traf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c by 2019 [1]. It will be enormous strain on already overburdened mobile networks to meet this big multimedia data demand, which drives mobile network operators to innovate new pricing schemes. Smart data pricing (SDP) [2] is likely to emerge as an effective way to in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬂ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">uence the user behavior in utilizing network resources. However, multimedia smart pricing has largely been ignored in literature. In this paper, we propose a fundamentally new framework named Smart Media Pricing (SMP) to allocate different prices to dif
+... [另一次引用] ...
+e State Scholarship Fund. REFERENCES [1] Cisco, Cisco Visual Networking Index, “Global mobile data traf </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ﬁ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c forecast update 2014 2019. white paper c11 520862,” Avail able on http://www. cisco. com/c/en/us/solutions/collateral/service provider/visual networking index vni/white paper c11 520862. html. [2] S. Sen, C. Joe Wong, S. Ha, and M. Chiang, “Smart data pricing (SDP): economic solutions to network congestion,” ACM SIGCOMM Recent Advances in Networking, pp. 221 274, 2013. [3] A. Mas Colell, M. D. Whinston, J. R. Green et al., Microeconomic theory. Oxford university press New York, 1995, vol. 1.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1520,7 +2763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1546,6 +2789,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1556,6 +2806,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="161"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1999,10 +3262,10 @@
         <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>27</v>
@@ -2026,16 +3289,16 @@
         <v>33</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="S2" s="3">
         <v>0.5</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
@@ -2055,16 +3318,16 @@
         <v>39</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>397</v>
+        <v>40</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>398</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>392</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>27</v>
@@ -2085,48 +3348,48 @@
         <v>42</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>43</v>
+        <v>391</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>394</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>50</v>
+        <v>395</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>393</v>
+        <v>49</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>27</v>
@@ -2144,201 +3407,225 @@
         <v>31</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.5</v>
+      </c>
       <c r="T4" s="2" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>396</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>59</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0.25</v>
+      </c>
       <c r="T5" s="2" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>71</v>
+        <v>397</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
+      <c r="Q6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0.25</v>
+      </c>
       <c r="T6" s="2" t="s">
-        <v>34</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0.75</v>
+      </c>
       <c r="T7" s="2" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>25</v>
@@ -2347,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>92</v>
+        <v>405</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>92</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>28</v>
@@ -2365,51 +3652,57 @@
         <v>30</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0.25</v>
+      </c>
       <c r="T8" s="2" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>100</v>
+        <v>408</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>28</v>
@@ -2421,51 +3714,57 @@
         <v>29</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0.75</v>
+      </c>
       <c r="T9" s="2" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>28</v>
@@ -2477,51 +3776,57 @@
         <v>29</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0.5</v>
+      </c>
       <c r="T10" s="2" t="s">
-        <v>34</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>28</v>
@@ -2533,13 +3838,13 @@
         <v>29</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -2550,34 +3855,34 @@
     </row>
     <row r="12" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>28</v>
@@ -2589,13 +3894,13 @@
         <v>29</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -2606,19 +3911,19 @@
     </row>
     <row r="13" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>40</v>
@@ -2627,31 +3932,31 @@
         <v>26</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -2662,34 +3967,34 @@
     </row>
     <row r="14" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>28</v>
@@ -2701,13 +4006,13 @@
         <v>29</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -2718,19 +4023,19 @@
     </row>
     <row r="15" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>25</v>
@@ -2739,13 +4044,13 @@
         <v>26</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>28</v>
@@ -2757,13 +4062,13 @@
         <v>29</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -2774,34 +4079,34 @@
     </row>
     <row r="16" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>28</v>
@@ -2810,16 +4115,16 @@
         <v>29</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2830,34 +4135,34 @@
     </row>
     <row r="17" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>28</v>
@@ -2866,16 +4171,16 @@
         <v>29</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -2886,34 +4191,34 @@
     </row>
     <row r="18" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>28</v>
@@ -2922,16 +4227,16 @@
         <v>29</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -2942,34 +4247,34 @@
     </row>
     <row r="19" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>28</v>
@@ -2978,16 +4283,16 @@
         <v>29</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -2998,34 +4303,34 @@
     </row>
     <row r="20" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>28</v>
@@ -3037,13 +4342,13 @@
         <v>30</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -3054,34 +4359,34 @@
     </row>
     <row r="21" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>28</v>
@@ -3093,13 +4398,13 @@
         <v>30</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -3110,34 +4415,34 @@
     </row>
     <row r="22" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>28</v>
@@ -3149,13 +4454,13 @@
         <v>30</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -3166,34 +4471,34 @@
     </row>
     <row r="23" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>28</v>
@@ -3205,13 +4510,13 @@
         <v>30</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -3222,10 +4527,10 @@
     </row>
     <row r="24" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>23</v>
@@ -3243,13 +4548,13 @@
         <v>26</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>28</v>
@@ -3261,13 +4566,13 @@
         <v>30</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -3278,34 +4583,34 @@
     </row>
     <row r="25" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>28</v>
@@ -3317,13 +4622,13 @@
         <v>30</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -3334,34 +4639,34 @@
     </row>
     <row r="26" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>28</v>
@@ -3373,13 +4678,13 @@
         <v>30</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -3390,34 +4695,34 @@
     </row>
     <row r="27" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>28</v>
@@ -3429,13 +4734,13 @@
         <v>30</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -3446,19 +4751,19 @@
     </row>
     <row r="28" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>25</v>
@@ -3467,13 +4772,13 @@
         <v>26</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>28</v>
@@ -3485,13 +4790,13 @@
         <v>30</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -3502,34 +4807,34 @@
     </row>
     <row r="29" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>28</v>
@@ -3538,16 +4843,16 @@
         <v>29</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -3558,34 +4863,34 @@
     </row>
     <row r="30" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>28</v>
@@ -3597,13 +4902,13 @@
         <v>29</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -3614,34 +4919,34 @@
     </row>
     <row r="31" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>28</v>
@@ -3653,13 +4958,13 @@
         <v>29</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -3670,34 +4975,34 @@
     </row>
     <row r="32" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>28</v>
@@ -3709,13 +5014,13 @@
         <v>29</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -3726,34 +5031,34 @@
     </row>
     <row r="33" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>28</v>
@@ -3765,13 +5070,13 @@
         <v>29</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -3782,34 +5087,34 @@
     </row>
     <row r="34" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>28</v>
@@ -3821,13 +5126,13 @@
         <v>29</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -3838,19 +5143,19 @@
     </row>
     <row r="35" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>25</v>
@@ -3859,13 +5164,13 @@
         <v>26</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>28</v>
@@ -3877,13 +5182,13 @@
         <v>29</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -3894,19 +5199,19 @@
     </row>
     <row r="36" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>25</v>
@@ -3915,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>28</v>
@@ -3933,13 +5238,13 @@
         <v>29</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -3950,34 +5255,34 @@
     </row>
     <row r="37" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>28</v>
@@ -3989,13 +5294,13 @@
         <v>29</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -4006,34 +5311,34 @@
     </row>
     <row r="38" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>28</v>
@@ -4045,13 +5350,13 @@
         <v>29</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4062,34 +5367,34 @@
     </row>
     <row r="39" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>28</v>
@@ -4101,13 +5406,13 @@
         <v>29</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -4118,34 +5423,34 @@
     </row>
     <row r="40" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>28</v>
@@ -4157,13 +5462,13 @@
         <v>29</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
@@ -4174,34 +5479,34 @@
     </row>
     <row r="41" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>28</v>
@@ -4213,13 +5518,13 @@
         <v>29</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
@@ -4230,52 +5535,52 @@
     </row>
     <row r="42" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H42" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="P42" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -4286,19 +5591,19 @@
     </row>
     <row r="43" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>40</v>
@@ -4307,16 +5612,16 @@
         <v>26</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>29</v>
@@ -4325,13 +5630,13 @@
         <v>29</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -4342,37 +5647,37 @@
     </row>
     <row r="44" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>29</v>
@@ -4381,13 +5686,13 @@
         <v>29</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
@@ -4398,52 +5703,52 @@
     </row>
     <row r="45" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="P45" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -4454,52 +5759,52 @@
     </row>
     <row r="46" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P46" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
@@ -4510,52 +5815,52 @@
     </row>
     <row r="47" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="O47" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K47" s="2" t="s">
+      <c r="P47" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
@@ -4566,52 +5871,52 @@
     </row>
     <row r="48" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="O48" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="P48" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
@@ -4622,52 +5927,52 @@
     </row>
     <row r="49" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>29</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
@@ -4678,52 +5983,52 @@
     </row>
     <row r="50" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="O50" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="P50" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
@@ -4734,52 +6039,52 @@
     </row>
     <row r="51" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="P51" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
